--- a/backend/src/mapping/templates/Vendor.xlsx
+++ b/backend/src/mapping/templates/Vendor.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416"/>
   </bookViews>
   <sheets>
-    <sheet name="Vendor" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Vendor" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="109">
   <si>
     <t>Display Name</t>
   </si>
@@ -169,6 +169,45 @@
     <t>Bank Account Number</t>
   </si>
   <si>
+    <t>Conact Salutation</t>
+  </si>
+  <si>
+    <t>Contact First Name</t>
+  </si>
+  <si>
+    <t>Conact Last Name</t>
+  </si>
+  <si>
+    <t>Conact Display Name</t>
+  </si>
+  <si>
+    <t>Conact EmailID</t>
+  </si>
+  <si>
+    <t>Conact Phone</t>
+  </si>
+  <si>
+    <t>Conact MobilePhone</t>
+  </si>
+  <si>
+    <t>Conact Skype</t>
+  </si>
+  <si>
+    <t>Conact Department</t>
+  </si>
+  <si>
+    <t>Conact Designation</t>
+  </si>
+  <si>
+    <t>Account Holder Name</t>
+  </si>
+  <si>
+    <t>IFS Code</t>
+  </si>
+  <si>
+    <t>SWIFT Code</t>
+  </si>
+  <si>
     <t>Ethan</t>
   </si>
   <si>
@@ -223,6 +262,24 @@
     <t>ABC BANK</t>
   </si>
   <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Peter</t>
+  </si>
+  <si>
+    <t>Flashter Inc.</t>
+  </si>
+  <si>
+    <t>john.peter@zylker.org</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Sales Executive</t>
+  </si>
+  <si>
     <t>Ganesh</t>
   </si>
   <si>
@@ -256,6 +313,21 @@
     <t>194H</t>
   </si>
   <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>smith.robert@zylker.org</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
     <t>Ram</t>
   </si>
   <si>
@@ -269,393 +341,30 @@
   </si>
   <si>
     <t>34GSPTN0372G1ZD</t>
-  </si>
-  <si>
-    <t>Conact Salutation</t>
-  </si>
-  <si>
-    <t>Contact First Name</t>
-  </si>
-  <si>
-    <t>Conact Last Name</t>
-  </si>
-  <si>
-    <t>Conact Display Name</t>
-  </si>
-  <si>
-    <t>Conact EmailID</t>
-  </si>
-  <si>
-    <t>Conact Phone</t>
-  </si>
-  <si>
-    <t>Conact MobilePhone</t>
-  </si>
-  <si>
-    <t>Conact Skype</t>
-  </si>
-  <si>
-    <t>Conact Department</t>
-  </si>
-  <si>
-    <t>Conact Designation</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Peter</t>
-  </si>
-  <si>
-    <t>Flashter Inc.</t>
-  </si>
-  <si>
-    <t>john.peter@zylker.org</t>
-  </si>
-  <si>
-    <t>Sales</t>
-  </si>
-  <si>
-    <t>Sales Executive</t>
-  </si>
-  <si>
-    <t>Smith</t>
-  </si>
-  <si>
-    <t>Robert</t>
-  </si>
-  <si>
-    <t>smith.robert@zylker.org</t>
-  </si>
-  <si>
-    <t>Management</t>
-  </si>
-  <si>
-    <t>Manager</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -663,204 +372,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1172,10 +692,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BI4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:BL4"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1330,60 +850,69 @@
         <v>50</v>
       </c>
       <c r="AZ1" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="BA1" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="BB1" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="BC1" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="BD1" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="BE1" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="BF1" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="BG1" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="BH1" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="BI1" t="s">
-        <v>94</v>
+        <v>60</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="G2" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H2" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="K2">
         <f>91-8870312457</f>
@@ -1393,52 +922,52 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="T2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="U2" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="V2" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="W2" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="Y2" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="AA2" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="AB2" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="AD2">
         <v>6000030</v>
       </c>
       <c r="AH2" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="AJ2" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="AK2" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="AL2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="AM2">
         <v>6000030</v>
       </c>
       <c r="AU2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="AV2">
         <v>194</v>
@@ -1447,61 +976,61 @@
         <v>10</v>
       </c>
       <c r="AX2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="AY2">
         <v>411111111111</v>
       </c>
       <c r="AZ2" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="BA2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="BB2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="BC2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="BD2" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="BE2">
         <f>27-712315678</f>
         <v>-712315651</v>
       </c>
       <c r="BH2" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="BI2" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" t="s">
         <v>69</v>
       </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
-      </c>
       <c r="G3" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="J3">
         <f>1-5417543010</f>
@@ -1511,16 +1040,16 @@
         <v>-2</v>
       </c>
       <c r="Q3" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="S3" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="U3" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="V3" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="AR3">
         <v>1400</v>
@@ -1529,60 +1058,60 @@
         <v>1</v>
       </c>
       <c r="AU3" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AV3" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="AW3">
         <v>5</v>
       </c>
       <c r="AZ3" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="BA3" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>100</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>84</v>
+      </c>
+      <c r="BD3" t="s">
         <v>101</v>
       </c>
-      <c r="BB3" t="s">
+      <c r="BH3" t="s">
         <v>102</v>
       </c>
-      <c r="BC3" t="s">
-        <v>97</v>
-      </c>
-      <c r="BD3" t="s">
+      <c r="BI3" t="s">
         <v>103</v>
       </c>
-      <c r="BH3" t="s">
+    </row>
+    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>104</v>
       </c>
-      <c r="BI3" t="s">
+      <c r="B4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="4" spans="1:61" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" t="s">
-        <v>81</v>
-      </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="G4" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="J4">
         <f>91-9870312457</f>
@@ -1592,16 +1121,16 @@
         <v>-3</v>
       </c>
       <c r="Q4" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="S4" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="U4" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="V4" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="AR4">
         <v>1400</v>
@@ -1610,10 +1139,10 @@
         <v>1</v>
       </c>
       <c r="AU4" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AV4" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="AW4">
         <v>5</v>
